--- a/script/catalogo_actualizado.xlsx
+++ b/script/catalogo_actualizado.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Documents\catalogo-motos-main\catalogo-motos\script\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A895665-85C8-4D2E-9678-54FB91C06DDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CBC98B1-5068-42B2-9F38-C745CB7647E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-135" yWindow="-135" windowWidth="29070" windowHeight="15750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
